--- a/tests/fixtures/excel/loi-sai-cot.xlsx
+++ b/tests/fixtures/excel/loi-sai-cot.xlsx
@@ -425,7 +425,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ngày vào Đảng chính thức</t>
+          <t>Ngày vào Đảng (dự bị)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
